--- a/artfynd/A 42982-2025 artfynd.xlsx
+++ b/artfynd/A 42982-2025 artfynd.xlsx
@@ -758,6 +758,16 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -845,6 +855,16 @@
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -932,6 +952,16 @@
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1019,6 +1049,16 @@
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1106,6 +1146,16 @@
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1193,6 +1243,16 @@
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fredrika Becker</t>
+        </is>
+      </c>
       <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 42982-2025 artfynd.xlsx
+++ b/artfynd/A 42982-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910402</v>
       </c>
       <c r="B2" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129910404</v>
       </c>
       <c r="B3" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129910406</v>
       </c>
       <c r="B4" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129910407</v>
       </c>
       <c r="B5" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129910405</v>
       </c>
       <c r="B6" t="n">
-        <v>78747</v>
+        <v>78750</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129910403</v>
       </c>
       <c r="B7" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42982-2025 artfynd.xlsx
+++ b/artfynd/A 42982-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910402</v>
       </c>
       <c r="B2" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129910404</v>
       </c>
       <c r="B3" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129910406</v>
       </c>
       <c r="B4" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129910407</v>
       </c>
       <c r="B5" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129910405</v>
       </c>
       <c r="B6" t="n">
-        <v>78750</v>
+        <v>78753</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129910403</v>
       </c>
       <c r="B7" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42982-2025 artfynd.xlsx
+++ b/artfynd/A 42982-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910402</v>
       </c>
       <c r="B2" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129910404</v>
       </c>
       <c r="B3" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129910406</v>
       </c>
       <c r="B4" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129910407</v>
       </c>
       <c r="B5" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129910405</v>
       </c>
       <c r="B6" t="n">
-        <v>78753</v>
+        <v>78754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129910403</v>
       </c>
       <c r="B7" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42982-2025 artfynd.xlsx
+++ b/artfynd/A 42982-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910402</v>
       </c>
       <c r="B2" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129910404</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129910406</v>
       </c>
       <c r="B4" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129910407</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129910405</v>
       </c>
       <c r="B6" t="n">
-        <v>78754</v>
+        <v>78755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129910403</v>
       </c>
       <c r="B7" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42982-2025 artfynd.xlsx
+++ b/artfynd/A 42982-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910402</v>
       </c>
       <c r="B2" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42982-2025 artfynd.xlsx
+++ b/artfynd/A 42982-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910402</v>
       </c>
       <c r="B2" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129910404</v>
       </c>
       <c r="B3" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129910406</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129910407</v>
       </c>
       <c r="B5" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129910405</v>
       </c>
       <c r="B6" t="n">
-        <v>78761</v>
+        <v>78846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129910403</v>
       </c>
       <c r="B7" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42982-2025 artfynd.xlsx
+++ b/artfynd/A 42982-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910402</v>
       </c>
       <c r="B2" t="n">
-        <v>93010</v>
+        <v>92923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129910404</v>
       </c>
       <c r="B3" t="n">
-        <v>78938</v>
+        <v>78853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129910406</v>
       </c>
       <c r="B4" t="n">
-        <v>79770</v>
+        <v>79685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129910407</v>
       </c>
       <c r="B5" t="n">
-        <v>78938</v>
+        <v>78853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129910405</v>
       </c>
       <c r="B6" t="n">
-        <v>78846</v>
+        <v>78761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129910403</v>
       </c>
       <c r="B7" t="n">
-        <v>79799</v>
+        <v>79714</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42982-2025 artfynd.xlsx
+++ b/artfynd/A 42982-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129910402</v>
+        <v>129910405</v>
       </c>
       <c r="B2" t="n">
-        <v>93010</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490577</v>
+        <v>490560</v>
       </c>
       <c r="R2" t="n">
-        <v>6876784</v>
+        <v>6876757</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910404</v>
+        <v>129910402</v>
       </c>
       <c r="B3" t="n">
-        <v>78938</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490578</v>
+        <v>490577</v>
       </c>
       <c r="R3" t="n">
-        <v>6876782</v>
+        <v>6876784</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910406</v>
+        <v>129910403</v>
       </c>
       <c r="B4" t="n">
-        <v>79770</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490566</v>
+        <v>490577</v>
       </c>
       <c r="R4" t="n">
-        <v>6876750</v>
+        <v>6876784</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129910407</v>
+        <v>129910404</v>
       </c>
       <c r="B5" t="n">
-        <v>78938</v>
+        <v>79085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490650</v>
+        <v>490578</v>
       </c>
       <c r="R5" t="n">
-        <v>6876763</v>
+        <v>6876782</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129910405</v>
+        <v>129910407</v>
       </c>
       <c r="B6" t="n">
-        <v>78846</v>
+        <v>79085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490560</v>
+        <v>490650</v>
       </c>
       <c r="R6" t="n">
-        <v>6876757</v>
+        <v>6876763</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129910403</v>
+        <v>129910406</v>
       </c>
       <c r="B7" t="n">
-        <v>79799</v>
+        <v>79917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490577</v>
+        <v>490566</v>
       </c>
       <c r="R7" t="n">
-        <v>6876784</v>
+        <v>6876750</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1245,12 +1245,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrika Becker</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 42982-2025 artfynd.xlsx
+++ b/artfynd/A 42982-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910405</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910402</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910403</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910404</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910407</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910406</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>